--- a/report-template.xlsx
+++ b/report-template.xlsx
@@ -106,6 +106,13 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="16"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -115,13 +122,6 @@
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF2A6099"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -187,40 +187,40 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -249,11 +249,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -268,7 +264,7 @@
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Accent" xfId="20"/>
+    <cellStyle name="Accent 4" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -331,54 +327,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>564840</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>114840</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>707040</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>177840</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Image 1" descr="&#10;    Stats Report Streamline Icon: https://streamlinehq.com&#10;  "/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="564840" y="114840"/>
-          <a:ext cx="955080" cy="955080"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -496,70 +444,70 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="14.05" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -571,26 +519,26 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
@@ -621,14 +569,14 @@
       <c r="H11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
@@ -661,26 +609,26 @@
       <c r="H14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
@@ -693,7 +641,7 @@
       </c>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="6" t="s">
@@ -707,452 +655,452 @@
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
-      <c r="G18" s="8"/>
+      <c r="G18" s="14"/>
       <c r="H18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="1"/>
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="1"/>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
     </row>
     <row r="24" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
     </row>
     <row r="25" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
     </row>
     <row r="31" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
     </row>
     <row r="32" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
     </row>
     <row r="34" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
     </row>
     <row r="35" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
     </row>
     <row r="44" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
     </row>
     <row r="45" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
     </row>
     <row r="46" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
     </row>
     <row r="47" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
     </row>
     <row r="48" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
     </row>
     <row r="50" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
     </row>
     <row r="51" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
+      <c r="A51" s="2"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="H51" s="2"/>
     </row>
     <row r="52" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
+      <c r="A52" s="2"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
     </row>
     <row r="53" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="H53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
+      <c r="A54" s="2"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="16"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
-      <c r="H56" s="16"/>
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="15"/>
+      <c r="E56" s="15"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15"/>
+      <c r="H56" s="15"/>
     </row>
     <row r="57" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="16"/>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
+      <c r="E57" s="15"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
     </row>
     <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="16"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
-      <c r="H58" s="16"/>
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="15"/>
+      <c r="E58" s="15"/>
+      <c r="F58" s="15"/>
+      <c r="G58" s="15"/>
+      <c r="H58" s="15"/>
     </row>
     <row r="59" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="16"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="16"/>
+      <c r="A59" s="15"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
     </row>
     <row r="60" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="16"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="16"/>
-      <c r="H60" s="16"/>
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="15"/>
+      <c r="E60" s="15"/>
+      <c r="F60" s="15"/>
+      <c r="G60" s="15"/>
+      <c r="H60" s="15"/>
     </row>
     <row r="61" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="16"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="16"/>
-      <c r="G61" s="16"/>
-      <c r="H61" s="16"/>
+      <c r="A61" s="15"/>
+      <c r="B61" s="15"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="15"/>
+      <c r="E61" s="15"/>
+      <c r="F61" s="15"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
     </row>
     <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="16"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="F62" s="16"/>
-      <c r="G62" s="16"/>
-      <c r="H62" s="16"/>
+      <c r="A62" s="15"/>
+      <c r="B62" s="15"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="15"/>
+      <c r="E62" s="15"/>
+      <c r="F62" s="15"/>
+      <c r="G62" s="15"/>
+      <c r="H62" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C1:H6"/>
+    <mergeCell ref="A1:H6"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:G10"/>
     <mergeCell ref="B11:C11"/>
@@ -1162,9 +1110,9 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D17:G17"/>
     <mergeCell ref="A18:C18"/>
-    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D18:G18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.39375" right="0.39375" top="0.39375" bottom="0.39375" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1173,6 +1121,5 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>